--- a/main/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T09:33:49+00:00</t>
+    <t>2026-03-30T15:11:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T15:11:58+00:00</t>
+    <t>2026-03-31T07:16:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T07:16:03+00:00</t>
+    <t>2026-04-01T07:43:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T07:43:12+00:00</t>
+    <t>2026-04-02T07:21:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T07:21:27+00:00</t>
+    <t>2026-04-02T12:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T12:41:19+00:00</t>
+    <t>2026-04-07T08:23:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T08:23:13+00:00</t>
+    <t>2026-04-15T13:29:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T13:29:57+00:00</t>
+    <t>2026-04-15T15:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T15:41:19+00:00</t>
+    <t>2026-04-20T15:11:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -5214,7 +5214,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
         <v>175</v>
       </c>
@@ -5233,7 +5233,7 @@
         <v>75</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>74</v>
+        <v>168</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>74</v>
@@ -5618,7 +5618,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
         <v>183</v>
       </c>
@@ -5633,13 +5633,13 @@
         <v>62</v>
       </c>
       <c r="F43" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>74</v>
+        <v>168</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>74</v>
@@ -5721,7 +5721,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
         <v>186</v>
       </c>
@@ -5736,13 +5736,13 @@
         <v>187</v>
       </c>
       <c r="F44" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>74</v>
+        <v>168</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>74</v>
@@ -6030,7 +6030,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
         <v>198</v>
       </c>
@@ -6051,7 +6051,7 @@
         <v>75</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>74</v>
+        <v>168</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>74</v>

--- a/main/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:11:12+00:00</t>
+    <t>2026-04-23T15:25:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T15:25:59+00:00</t>
+    <t>2026-05-06T07:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T07:44:21+00:00</t>
+    <t>2026-05-13T14:53:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:53:03+00:00</t>
+    <t>2026-05-15T08:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:35:10+00:00</t>
+    <t>2026-06-29T12:53:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:53:00+00:00</t>
+    <t>2026-06-29T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -805,8 +805,8 @@
     <t>Observation.value</t>
   </si>
   <si>
-    <t>http://hl7.org/cda/stds/core/StructureDefinition/ANY
-http://hl7.org/cda/stds/core/StructureDefinition/BLhttp://hl7.org/cda/stds/core/StructureDefinition/EDhttp://hl7.org/cda/stds/core/StructureDefinition/SThttp://hl7.org/cda/stds/core/StructureDefinition/CDhttp://hl7.org/cda/stds/core/StructureDefinition/CVhttp://hl7.org/cda/stds/core/StructureDefinition/CEhttp://hl7.org/cda/stds/core/StructureDefinition/COhttp://hl7.org/cda/stds/core/StructureDefinition/SChttp://hl7.org/cda/stds/core/StructureDefinition/IIhttp://hl7.org/cda/stds/core/StructureDefinition/TELhttp://hl7.org/cda/stds/core/StructureDefinition/ADhttp://hl7.org/cda/stds/core/StructureDefinition/ENhttp://hl7.org/cda/stds/core/StructureDefinition/INThttp://hl7.org/cda/stds/core/StructureDefinition/REALhttp://hl7.org/cda/stds/core/StructureDefinition/PQhttp://hl7.org/cda/stds/core/StructureDefinition/MOhttp://hl7.org/cda/stds/core/StructureDefinition/TShttp://hl7.org/cda/stds/core/StructureDefinition/IVL-PQhttp://hl7.org/cda/stds/core/StructureDefinition/IVL-TShttp://hl7.org/cda/stds/core/StructureDefinition/PIVL-TShttp://hl7.org/cda/stds/core/StructureDefinition/EIVL-TShttp://hl7.org/cda/stds/core/StructureDefinition/SXPR-TShttp://hl7.org/cda/stds/core/StructureDefinition/RTO-PQ-PQ</t>
+    <t>http://hl7.org/cda/stds/core/StructureDefinition/CD
+http://hl7.org/cda/stds/core/StructureDefinition/PQhttp://hl7.org/cda/stds/core/StructureDefinition/SThttp://hl7.org/cda/stds/core/StructureDefinition/ADhttp://hl7.org/cda/stds/core/StructureDefinition/BLhttp://hl7.org/cda/stds/core/StructureDefinition/CEhttp://hl7.org/cda/stds/core/StructureDefinition/COhttp://hl7.org/cda/stds/core/StructureDefinition/CShttp://hl7.org/cda/stds/core/StructureDefinition/CVhttp://hl7.org/cda/stds/core/StructureDefinition/EDhttp://hl7.org/cda/stds/core/StructureDefinition/ENhttp://hl7.org/cda/stds/core/StructureDefinition/IIhttp://hl7.org/cda/stds/core/StructureDefinition/INThttp://hl7.org/cda/stds/core/StructureDefinition/INT-POShttp://hl7.org/cda/stds/core/StructureDefinition/MOhttp://hl7.org/cda/stds/core/StructureDefinition/ONhttp://hl7.org/cda/stds/core/StructureDefinition/PNhttp://hl7.org/cda/stds/core/StructureDefinition/REALhttp://hl7.org/cda/stds/core/StructureDefinition/SChttp://hl7.org/cda/stds/core/StructureDefinition/TELhttp://hl7.org/cda/stds/core/StructureDefinition/TNhttp://hl7.org/cda/stds/core/StructureDefinition/TShttp://hl7.org/cda/stds/core/StructureDefinition/IVL-INThttp://hl7.org/cda/stds/core/StructureDefinition/IVL-PQhttp://hl7.org/cda/stds/core/StructureDefinition/IVL-TShttp://hl7.org/cda/stds/core/StructureDefinition/PIVL-TShttp://hl7.org/cda/stds/core/StructureDefinition/EIVL-TShttp://hl7.org/cda/stds/core/StructureDefinition/SXPR-TShttp://hl7.org/cda/stds/core/StructureDefinition/RTO-PQ-PQ</t>
   </si>
   <si>
     <t>Résultat de l'observation effectuéee</t>

--- a/main/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:20:03+00:00</t>
+    <t>2026-06-29T15:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T15:28:29+00:00</t>
+    <t>2026-06-30T08:01:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:01:58+00:00</t>
+    <t>2026-06-30T09:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:01:37+00:00</t>
+    <t>2026-06-30T09:56:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-habitus-mode-de-vie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:56:22+00:00</t>
+    <t>2026-08-06T11:33:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
